--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9726311-A060-4A0C-ACB2-44D217833226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0291F616-FEDF-4878-96B9-C3F634B96A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="課題一覧" sheetId="1" r:id="rId1"/>
@@ -1210,7 +1210,9 @@
       <c r="D15" s="14">
         <v>46158</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="14">
+        <v>46288</v>
+      </c>
       <c r="F15" s="15">
         <v>46292</v>
       </c>
